--- a/banks/W03_Kahoot匯入.xlsx
+++ b/banks/W03_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>胜肽鍵</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>雙硫鍵</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>胺基酸</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>多肽</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>胜肽鍵</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>雙硫鍵</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>N端</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>層析</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>多肽</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>N端</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>胺基</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>電泳</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>多肽</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>胺基</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>電泳</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>胺基</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>羧基</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>手性</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>羧基</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>胺基</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>手性</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>胺基</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>多肽</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>層析</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>胺基</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>多肽</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>手性</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>多肽</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>羧基</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>胜肽</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>層析</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>多肽</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>胜肽</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>芳香族</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>C端</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>胜肽鍵</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>芳香族</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>N端</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>羧基</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>多肽</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>羧基</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>N端</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>C端</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -771,30 +771,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>C端</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>胜肽</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>手性</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>N端</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>C端</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>胜肽</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>手性</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -806,22 +806,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>電泳</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>C端</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>羧基</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>C端</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>N端</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>電泳</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,17 +841,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>芳香族</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>兩性離子</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>胺基</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>兩性離子</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>芳香族</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>胜肽鍵</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>胺基酸</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>胺基</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>等電點</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>胜肽鍵</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>多肽</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>雙硫鍵</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>等電點</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>多肽</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>雙硫鍵</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -946,19 +946,19 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>芳香族</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>胜肽</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>手性</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>芳香族</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>胜肽</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>胺基酸</t>
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>兩性離子</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>電泳</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>雙硫鍵</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>羧基</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>兩性離子</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>電泳</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>手性</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>多肽</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>層析</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>手性</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>多肽</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>電泳</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,170 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>電泳</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>N端</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>層析</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>N端</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>羧基</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>電泳</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:胜肽鍵形成) 標號3(黃色框)是什麼鍵?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>胜肽鍵</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>雙硫鍵</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>離子鍵</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:胺基酸通用結構) 標號2指的是什麼?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>側鏈</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>胺基</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>羧基</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>α碳</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>胜肽鍵—連接兩個醣類</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>N端—胺基那一端</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>C端—胺基那一端</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>側鏈—讓所有胺基酸都一樣</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>決定不同胺基酸性質差異的部分是什麼?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>側鏈</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>羧基</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>胺基</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>α碳</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
